--- a/qqid.xlsx
+++ b/qqid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -497,11 +497,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[454, 'B']</t>
+          <t>[83, 'A']</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1722272128.26183</v>
+        <v>1723362634.620575</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1722305698.775858</v>
+        <v>1722305698.77586</v>
       </c>
     </row>
     <row r="4">
@@ -555,17 +555,21 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>zhiliye</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>Zhiliye</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Zhiliye</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>[221, 'B']</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1722240307.467367</v>
+        <v>1722240307.46737</v>
       </c>
     </row>
     <row r="5">
@@ -674,20 +678,28 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Proaes</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meluam</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Proaes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Proaes</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>[439, 'B']</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1722231897.346222</v>
+        <v>1722231897.34622</v>
       </c>
     </row>
     <row r="10">
@@ -720,13 +732,21 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Komeiji_Satori</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Icyecho</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>冘木</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -809,6 +829,170 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1831944862</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sakuya_maid</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sakuya_maid</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sakuya_maid</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1075057793</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Yingwenyu</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yingwy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ywy1075057793</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3057155010</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>qh_only_one</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>whatiisname</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CJF2005cjf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2075958609</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ZGonce819</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3200262498</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nqw3200262498</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2171682519</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zzzzyyyy0703</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>875722864</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ariri</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
